--- a/TIMES-NZ/v303/SubRES_TMPL/SubRES_SectorClosures.xlsx
+++ b/TIMES-NZ/v303/SubRES_TMPL/SubRES_SectorClosures.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>METH-NGA-FDSTK-FDSTK-CLOSURE</t>
+          <t>Methanol-CLOSURE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>METH-NGA-REFRM-PH_HIGH-CLOSURE</t>
+          <t>Urea-CLOSURE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -508,250 +508,244 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>UREA-NGA-FDSTK-FDSTK-CLOSURE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>PJa</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>UREA-NGA-REFRM-PH_HIGH-CLOSURE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PJa</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SectorClosureParameters</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Sets parameters for sector closures, including costs and possible start dates</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DMD</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>UREA-NGA-COMPR-MTV_STA-CLOSURE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PJ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PJa</t>
+          <t>~FI_T</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Comm-Out</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Share-O</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ACTCOST</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LIFE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Share-O~0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SectorClosureParameters</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Sets parameters for sector closures, including costs and possible start dates</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Methanol-CLOSURE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>METH-FDSTK-FDSTK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.6323269332481042</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>~FI_T</t>
+          <t>Methanol-CLOSURE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>METH-REFRM-PH_HIGH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.3676730667518958</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TechName</t>
+          <t>Urea-CLOSURE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Comm-Out</t>
+          <t>UREA-FDSTK-FDSTK</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACTCOST</t>
+          <t>0.5824175824175825</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>START</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LIFE</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>METH-NGA-FDSTK-FDSTK-CLOSURE</t>
+          <t>Urea-CLOSURE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>METH-FDSTK-FDSTK</t>
+          <t>UREA-REFRM-PH_HIGH</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.269587272486444</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>100</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>METH-NGA-REFRM-PH_HIGH-CLOSURE</t>
+          <t>Urea-CLOSURE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>METH-REFRM-PH_HIGH</t>
+          <t>UREA-COMPR-MTV_STA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.1479951450959736</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>UREA-NGA-FDSTK-FDSTK-CLOSURE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>UREA-FDSTK-FDSTK</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>UREA-NGA-REFRM-PH_HIGH-CLOSURE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>UREA-REFRM-PH_HIGH</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>UREA-NGA-COMPR-MTV_STA-CLOSURE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>UREA-COMPR-MTV_STA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>100</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
